--- a/source_data/Supplementary_Figures/FigS7_SourceData.xlsx
+++ b/source_data/Supplementary_Figures/FigS7_SourceData.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>The full set of 1,247 target-role records (both roles; common-target curves in Fig. 4C): additive residual of the held-out pair against the profile of k randomly drawn training pairings of its molecule, five draws averaged (Fig4a_folds.csv, Fig4a_history_draws.csv). Explained = 1 - sum SSE_k / sum SST. Interval of R2(6) - R2(1): 2,000 resamples of the 150 array-role-molecule groups within arrays (exact resamples in FigS7_depth_interval_draws.csv); value of a resample = sum over its groups of (SSE_1 - SSE_6) / sum of SST; 2.5th and 97.5th percentiles (linear interpolation).</t>
+          <t>The full set of 1,247 target-role records (both roles; common-target curves in Fig. 5c): additive residual of the held-out pair against the profile of k randomly drawn training pairings of its molecule, five draws averaged (Fig4a_folds.csv, Fig4a_history_draws.csv). Explained = 1 - sum SSE_k / sum SST. Interval of R2(6) - R2(1): 2,000 resamples of the 150 array-role-molecule groups within arrays (exact resamples in FigS7_depth_interval_draws.csv); value of a resample = sum over its groups of (SSE_1 - SSE_6) / sum of SST; 2.5th and 97.5th percentiles (linear interpolation).</t>
         </is>
       </c>
     </row>
